--- a/src_files/data_files/unittypedata_compilation.xlsx
+++ b/src_files/data_files/unittypedata_compilation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8E5763-CDA7-4C2F-AF2E-6CE5A5EA4289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A6B275-1735-4A78-882E-C2D1A8BBE2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -754,18 +754,6 @@
     <t>A nuclear unit with much lower ramp costs for flexible part of countrys operation</t>
   </si>
   <si>
-    <t>disabled-rampUpCost</t>
-  </si>
-  <si>
-    <t>disabled-rampDownCost</t>
-  </si>
-  <si>
-    <t>disabled-maxRampUp</t>
-  </si>
-  <si>
-    <t>disabled-maxRampDown</t>
-  </si>
-  <si>
     <t>Assuming 3% losses in cell and 3% in inverter both directions (charge+discharge) for all BESS</t>
   </si>
   <si>
@@ -803,6 +791,18 @@
   </si>
   <si>
     <t>Note</t>
+  </si>
+  <si>
+    <t>##maxRampUp</t>
+  </si>
+  <si>
+    <t>##maxRampDown</t>
+  </si>
+  <si>
+    <t>##rampUpCost</t>
+  </si>
+  <si>
+    <t>##rampDownCost</t>
   </si>
 </sst>
 </file>
@@ -1278,10 +1278,10 @@
         <v>197</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>1</v>
@@ -1290,21 +1290,21 @@
         <v>100</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="AA1" s="3" t="s">
         <v>183</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="15"/>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="T3" s="19"/>
       <c r="AB3" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1429,7 +1429,7 @@
     </row>
     <row r="6" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="15"/>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="13" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="15"/>
@@ -3229,7 +3229,7 @@
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="9"/>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="9"/>
@@ -3509,7 +3509,7 @@
     </row>
     <row r="50" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="15"/>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="54" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="15"/>
@@ -3781,7 +3781,7 @@
         <v>4</v>
       </c>
       <c r="AB55" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3879,7 +3879,7 @@
     </row>
     <row r="59" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="15"/>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="83" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B83" s="18"/>
       <c r="C83" s="15"/>
@@ -5178,7 +5178,7 @@
     </row>
     <row r="89" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="15"/>

--- a/src_files/data_files/unittypedata_compilation.xlsx
+++ b/src_files/data_files/unittypedata_compilation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A6B275-1735-4A78-882E-C2D1A8BBE2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025226CE-07DA-49AD-A46B-B4FF1144D435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="302">
   <si>
     <t>vomCosts</t>
   </si>
@@ -82,9 +82,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Hard coal</t>
-  </si>
-  <si>
     <t>Hard coal old 1</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>Hard coal old 2 Bio</t>
   </si>
   <si>
-    <t>Lignite</t>
-  </si>
-  <si>
     <t>Lignite old 1</t>
   </si>
   <si>
@@ -127,9 +121,6 @@
     <t>Lignite old 2 Bio</t>
   </si>
   <si>
-    <t>Gas</t>
-  </si>
-  <si>
     <t>Gas conventional old 1</t>
   </si>
   <si>
@@ -163,18 +154,12 @@
     <t>Light oil</t>
   </si>
   <si>
-    <t>Heavy oil</t>
-  </si>
-  <si>
     <t>Heavy oil old 1</t>
   </si>
   <si>
     <t>Heavy oil old 2</t>
   </si>
   <si>
-    <t>Oil shale</t>
-  </si>
-  <si>
     <t>Oil shale old</t>
   </si>
   <si>
@@ -193,9 +178,6 @@
     <t>Gas HOB</t>
   </si>
   <si>
-    <t>Biomass</t>
-  </si>
-  <si>
     <t>Bio HOB</t>
   </si>
   <si>
@@ -205,9 +187,6 @@
     <t>Coal CHP</t>
   </si>
   <si>
-    <t>MSW</t>
-  </si>
-  <si>
     <t>Waste CHP</t>
   </si>
   <si>
@@ -247,9 +226,6 @@
     <t>Battery discharger</t>
   </si>
   <si>
-    <t>batterystor</t>
-  </si>
-  <si>
     <t>Battery charger</t>
   </si>
   <si>
@@ -262,9 +238,6 @@
     <t>PS Closed pump</t>
   </si>
   <si>
-    <t>hydrogen</t>
-  </si>
-  <si>
     <t>Hydrogen OCGT</t>
   </si>
   <si>
@@ -286,9 +259,6 @@
     <t>Heat storage discharger</t>
   </si>
   <si>
-    <t>heatsto</t>
-  </si>
-  <si>
     <t>Heat storage charger</t>
   </si>
   <si>
@@ -307,12 +277,6 @@
     <t>Seasonal heat storage discharger</t>
   </si>
   <si>
-    <t>largeheatsto</t>
-  </si>
-  <si>
-    <t>seasonheatsto</t>
-  </si>
-  <si>
     <t>Gas OCGT CHP</t>
   </si>
   <si>
@@ -334,12 +298,6 @@
     <t>Short-term hydrogen storage discharger</t>
   </si>
   <si>
-    <t>hydrogenstoLT</t>
-  </si>
-  <si>
-    <t>hydrogenstoST</t>
-  </si>
-  <si>
     <t>PS Open turbine</t>
   </si>
   <si>
@@ -688,12 +646,6 @@
     <t>oilshaleCHP</t>
   </si>
   <si>
-    <t>Generator_ID</t>
-  </si>
-  <si>
-    <t>ETS-CO2</t>
-  </si>
-  <si>
     <t>Coal HOB</t>
   </si>
   <si>
@@ -803,13 +755,232 @@
   </si>
   <si>
     <t>##rampDownCost</t>
+  </si>
+  <si>
+    <t>## Description</t>
+  </si>
+  <si>
+    <t>## old unittype</t>
+  </si>
+  <si>
+    <t>psOpenTurbine</t>
+  </si>
+  <si>
+    <t>psOpenPump</t>
+  </si>
+  <si>
+    <t>psClosedTurbine</t>
+  </si>
+  <si>
+    <t>psClosedPump</t>
+  </si>
+  <si>
+    <t>solarPV</t>
+  </si>
+  <si>
+    <t>wasteHOB</t>
+  </si>
+  <si>
+    <t>oilHOB</t>
+  </si>
+  <si>
+    <t>gasHOB</t>
+  </si>
+  <si>
+    <t>bioHOB</t>
+  </si>
+  <si>
+    <t>elecHOB</t>
+  </si>
+  <si>
+    <t>wasteCHP</t>
+  </si>
+  <si>
+    <t>coalCHP</t>
+  </si>
+  <si>
+    <t>coalOld2</t>
+  </si>
+  <si>
+    <t>coalOld1</t>
+  </si>
+  <si>
+    <t>coalNew</t>
+  </si>
+  <si>
+    <t>bioCHP</t>
+  </si>
+  <si>
+    <t>gasCCGTCHP</t>
+  </si>
+  <si>
+    <t>coalHOB</t>
+  </si>
+  <si>
+    <t>coalCHPExtraction</t>
+  </si>
+  <si>
+    <t>bioCHPExtraction</t>
+  </si>
+  <si>
+    <t>gasCHPExtraction</t>
+  </si>
+  <si>
+    <t>gasOCGTCHP</t>
+  </si>
+  <si>
+    <t>BatteryDisch4h</t>
+  </si>
+  <si>
+    <t>BatteryDisch</t>
+  </si>
+  <si>
+    <t>BatteryCharger4h</t>
+  </si>
+  <si>
+    <t>BatteryCharger</t>
+  </si>
+  <si>
+    <t>HeatStorageCharger</t>
+  </si>
+  <si>
+    <t>HeatStorageDisch</t>
+  </si>
+  <si>
+    <t>heatStorageChargerLarge</t>
+  </si>
+  <si>
+    <t>heatStorageDischLarge</t>
+  </si>
+  <si>
+    <t>heatStorageChargerSeasonal</t>
+  </si>
+  <si>
+    <t>heatStorageDischSeasonal</t>
+  </si>
+  <si>
+    <t>heatStor</t>
+  </si>
+  <si>
+    <t>heatStorL</t>
+  </si>
+  <si>
+    <t>heatStorXL</t>
+  </si>
+  <si>
+    <t>battery</t>
+  </si>
+  <si>
+    <t>battery4h</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>H2StorageDisch</t>
+  </si>
+  <si>
+    <t>H2StorageCharger</t>
+  </si>
+  <si>
+    <t>H2StorageDischLongterm</t>
+  </si>
+  <si>
+    <t>H2StorageChargerLongterm</t>
+  </si>
+  <si>
+    <t>H2Stor</t>
+  </si>
+  <si>
+    <t>H2StorL</t>
+  </si>
+  <si>
+    <t>coal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>oilShale</t>
+  </si>
+  <si>
+    <t>oilHeavy</t>
+  </si>
+  <si>
+    <t>waste</t>
+  </si>
+  <si>
+    <t>coalCCS</t>
+  </si>
+  <si>
+    <t>oilLight</t>
+  </si>
+  <si>
+    <t>OilLightOld</t>
+  </si>
+  <si>
+    <t>oilHeavyOld2</t>
+  </si>
+  <si>
+    <t>oilHeavyOld1</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>bioLigniteOld2</t>
+  </si>
+  <si>
+    <t>bioLigniteOld1</t>
+  </si>
+  <si>
+    <t>bioOilshaleNew</t>
+  </si>
+  <si>
+    <t>bioOilHeavyOld</t>
+  </si>
+  <si>
+    <t>bioCoalOld</t>
+  </si>
+  <si>
+    <t>bioCoalOld2</t>
+  </si>
+  <si>
+    <t>bioCoalNew</t>
+  </si>
+  <si>
+    <t>bioGasOld2</t>
+  </si>
+  <si>
+    <t>bioGasCCGTOld2</t>
+  </si>
+  <si>
+    <t>bioCHPIndustry</t>
+  </si>
+  <si>
+    <t>coalCHPIndustry</t>
+  </si>
+  <si>
+    <t>gasCHPIndustry</t>
+  </si>
+  <si>
+    <t>Hydrogen CCGT</t>
+  </si>
+  <si>
+    <t>hydrogenCCGT</t>
+  </si>
+  <si>
+    <t>ETS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -858,6 +1029,14 @@
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -928,11 +1107,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -987,8 +1167,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Standard_Data provided by OT3" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
@@ -1193,118 +1375,121 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB96"/>
+  <dimension ref="A1:AN97"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
     <col min="2" max="2" width="7.7109375" style="21" customWidth="1"/>
-    <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" customWidth="1"/>
     <col min="5" max="9" width="12.7109375" customWidth="1"/>
     <col min="10" max="10" width="16.5703125" customWidth="1"/>
     <col min="11" max="11" width="18.42578125" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" customWidth="1"/>
+    <col min="12" max="14" width="14.42578125" customWidth="1"/>
     <col min="15" max="16" width="12.7109375" customWidth="1"/>
     <col min="17" max="18" width="10.140625" customWidth="1"/>
     <col min="19" max="19" width="12.7109375" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" style="21" customWidth="1"/>
-    <col min="21" max="22" width="8.42578125" customWidth="1"/>
+    <col min="20" max="20" width="11.28515625" style="21" customWidth="1"/>
+    <col min="21" max="23" width="8.42578125" customWidth="1"/>
     <col min="25" max="26" width="14" customWidth="1"/>
     <col min="27" max="27" width="15.85546875" customWidth="1"/>
     <col min="28" max="28" width="78.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.28515625" customWidth="1"/>
     <col min="1024" max="1024" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="J1" s="7" t="s">
+      <c r="P1" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="Q1" s="3" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="T1" s="22" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="15"/>
@@ -1333,61 +1518,68 @@
       <c r="Z2" s="15"/>
       <c r="AA2" s="15"/>
       <c r="AB2" s="15"/>
-    </row>
-    <row r="3" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD2" s="15"/>
+    </row>
+    <row r="3" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B3" s="19">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O3" s="1">
         <v>1</v>
       </c>
       <c r="Q3" s="1">
         <v>1</v>
+      </c>
+      <c r="S3" s="1">
+        <v>1.75</v>
       </c>
       <c r="T3" s="19"/>
       <c r="AB3" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B4" s="19">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O4" s="1">
         <v>1</v>
@@ -1395,29 +1587,35 @@
       <c r="Q4" s="1">
         <v>1</v>
       </c>
+      <c r="S4" s="1">
+        <v>2</v>
+      </c>
       <c r="T4" s="19"/>
-    </row>
-    <row r="5" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD4" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>96</v>
+        <v>235</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O5" s="1">
         <v>1</v>
@@ -1425,11 +1623,17 @@
       <c r="Q5" s="1">
         <v>1</v>
       </c>
+      <c r="S5" s="1">
+        <v>1.5</v>
+      </c>
       <c r="T5" s="19"/>
-    </row>
-    <row r="6" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD5" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="15"/>
@@ -1458,25 +1662,26 @@
       <c r="Z6" s="15"/>
       <c r="AA6" s="15"/>
       <c r="AB6" s="15"/>
-    </row>
-    <row r="7" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD6" s="15"/>
+    </row>
+    <row r="7" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O7" s="1">
         <v>0.95</v>
@@ -1495,27 +1700,30 @@
         <v>5.5</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O8" s="1">
         <v>0.95</v>
@@ -1534,27 +1742,30 @@
         <v>5</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>159</v>
+        <v>231</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O9" s="1">
         <v>0.95</v>
@@ -1572,25 +1783,28 @@
       <c r="Z9" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD9" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B10" s="19">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>160</v>
+        <v>232</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O10" s="1">
         <v>0.8</v>
@@ -1608,25 +1822,28 @@
       <c r="Z10" s="1">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD10" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B11" s="19">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O11" s="1">
         <v>0.95</v>
@@ -1644,25 +1861,28 @@
       <c r="Z11" s="1">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="12" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD11" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B12" s="19">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>158</v>
+        <v>234</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="O12" s="1">
         <v>0.8</v>
@@ -1680,10 +1900,13 @@
       <c r="Z12" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD12" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="15"/>
@@ -1712,28 +1935,29 @@
       <c r="Z13" s="15"/>
       <c r="AA13" s="15"/>
       <c r="AB13" s="15"/>
-    </row>
-    <row r="14" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD13" s="15"/>
+    </row>
+    <row r="14" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B14" s="19">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>34</v>
+        <v>278</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O14" s="1">
         <v>0.26</v>
@@ -1763,28 +1987,31 @@
       <c r="Z14" s="1">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD14" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B15" s="19">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>141</v>
+        <v>289</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O15" s="1">
         <v>0.36</v>
@@ -1814,28 +2041,31 @@
       <c r="Z15" s="1">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD15" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B16" s="19">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>34</v>
+        <v>278</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O16" s="1">
         <v>0.36</v>
@@ -1865,26 +2095,29 @@
       <c r="Z16" s="1">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="17" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD16" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O17" s="1">
         <v>0.37</v>
@@ -1914,28 +2147,31 @@
       <c r="Z17" s="1">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="18" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD17" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B18" s="19">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>12</v>
+        <v>286</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O18" s="1">
         <v>0.37</v>
@@ -1965,26 +2201,29 @@
       <c r="Z18" s="1">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD18" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B19" s="19">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>114</v>
+        <v>288</v>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O19" s="1">
         <v>0.31999999999999995</v>
@@ -2014,28 +2253,31 @@
       <c r="Z19" s="1">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD19" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B20" s="19">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>12</v>
+        <v>286</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O20" s="1">
         <v>0.31999999999999995</v>
@@ -2065,28 +2307,31 @@
       <c r="Z20" s="1">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD20" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B21" s="19">
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>12</v>
+        <v>286</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O21" s="1">
         <v>0.43000000000000005</v>
@@ -2116,25 +2361,28 @@
       <c r="Z21" s="1">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="22" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD21" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B22" s="19">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>12</v>
+        <v>286</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O22" s="1">
         <v>0.35</v>
@@ -2164,28 +2412,31 @@
       <c r="Z22" s="1">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="23" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD22" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B23" s="19">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>136</v>
+        <v>283</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O23" s="1">
         <v>0.31999999999999995</v>
@@ -2215,28 +2466,31 @@
       <c r="Z23" s="1">
         <v>19.2</v>
       </c>
-    </row>
-    <row r="24" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD23" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B24" s="19">
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>138</v>
+        <v>284</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>31</v>
+        <v>279</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O24" s="1">
         <v>0.37</v>
@@ -2266,28 +2520,31 @@
       <c r="Z24" s="1">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD24" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B25" s="19">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>31</v>
+        <v>279</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O25" s="1">
         <v>0.31999999999999995</v>
@@ -2317,25 +2574,28 @@
       <c r="Z25" s="1">
         <v>47</v>
       </c>
-    </row>
-    <row r="26" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD25" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B26" s="19">
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>187</v>
+        <v>290</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O26" s="1">
         <v>0.28000000000000003</v>
@@ -2365,28 +2625,31 @@
       <c r="Z26" s="1">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="27" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD26" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B27" s="19">
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>120</v>
+        <v>291</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O27" s="1">
         <v>0.31999999999999995</v>
@@ -2416,28 +2679,31 @@
       <c r="Z27" s="13">
         <v>47</v>
       </c>
-    </row>
-    <row r="28" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD27" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B28" s="19">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>121</v>
+        <v>292</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O28" s="1">
         <v>0.37</v>
@@ -2467,28 +2733,31 @@
       <c r="Z28" s="1">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="29" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD28" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B29" s="19">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>117</v>
+        <v>243</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>4</v>
+        <v>275</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O29" s="1">
         <v>0.37</v>
@@ -2518,28 +2787,31 @@
       <c r="Z29" s="1">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="30" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD29" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B30" s="19">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>116</v>
+        <v>244</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>4</v>
+        <v>275</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O30" s="1">
         <v>0.31999999999999995</v>
@@ -2569,28 +2841,31 @@
       <c r="Z30" s="13">
         <v>47</v>
       </c>
-    </row>
-    <row r="31" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD30" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B31" s="19">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>119</v>
+        <v>293</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O31" s="1">
         <v>0.43000000000000005</v>
@@ -2620,28 +2895,31 @@
       <c r="Z31" s="1">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="32" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD31" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B32" s="19">
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>4</v>
+        <v>275</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O32" s="1">
         <v>0.43000000000000005</v>
@@ -2671,25 +2949,28 @@
       <c r="Z32" s="1">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="33" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD32" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B33" s="19">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O33" s="1">
         <v>0.27</v>
@@ -2719,28 +3000,31 @@
       <c r="Z33" s="1">
         <v>29.4</v>
       </c>
-    </row>
-    <row r="34" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD33" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B34" s="19">
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O34" s="1">
         <v>0.38</v>
@@ -2770,28 +3054,31 @@
       <c r="Z34" s="1">
         <v>29.4</v>
       </c>
-    </row>
-    <row r="35" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD34" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B35" s="19">
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O35" s="1">
         <v>0.32999999999999996</v>
@@ -2821,28 +3108,31 @@
       <c r="Z35" s="1">
         <v>34.799999999999997</v>
       </c>
-    </row>
-    <row r="36" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD35" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B36" s="19">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O36" s="1">
         <v>0.31999999999999995</v>
@@ -2872,28 +3162,31 @@
       <c r="Z36" s="1">
         <v>26.2</v>
       </c>
-    </row>
-    <row r="37" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD36" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B37" s="19">
         <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O37" s="1">
         <v>0.39</v>
@@ -2923,28 +3216,31 @@
       <c r="Z37" s="1">
         <v>12.1</v>
       </c>
-    </row>
-    <row r="38" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD37" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B38" s="19">
         <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O38" s="1">
         <v>0.54999999999999993</v>
@@ -2974,28 +3270,31 @@
       <c r="Z38" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="39" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD38" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B39" s="19">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O39" s="1">
         <v>0.53</v>
@@ -3025,25 +3324,28 @@
       <c r="Z39" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="40" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD39" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B40" s="19">
         <v>1</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O40" s="1">
         <v>0.29000000000000004</v>
@@ -3073,28 +3375,31 @@
       <c r="Z40" s="1">
         <v>30.9</v>
       </c>
-    </row>
-    <row r="41" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD40" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B41" s="19">
         <v>1</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O41" s="1">
         <v>0.44999999999999996</v>
@@ -3124,28 +3429,31 @@
       <c r="Z41" s="1">
         <v>30.9</v>
       </c>
-    </row>
-    <row r="42" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD41" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B42" s="19">
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O42" s="1">
         <v>0.37</v>
@@ -3175,28 +3483,31 @@
       <c r="Z42" s="1">
         <v>39.5</v>
       </c>
-    </row>
-    <row r="43" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD42" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B43" s="19">
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O43" s="1">
         <v>0.56999999999999995</v>
@@ -3226,10 +3537,13 @@
       <c r="Z43" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AD43" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="9"/>
@@ -3258,31 +3572,32 @@
       <c r="Z44" s="9"/>
       <c r="AA44" s="9"/>
       <c r="AB44" s="9"/>
-    </row>
-    <row r="45" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD44" s="9"/>
+    </row>
+    <row r="45" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B45" s="19">
         <v>1</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>178</v>
+        <v>281</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>4</v>
+        <v>275</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="M45" s="1">
         <v>0</v>
@@ -3315,31 +3630,34 @@
       <c r="Z45" s="1">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="46" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD45" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B46" s="19">
         <v>1</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="M46" s="1">
         <v>0</v>
@@ -3372,10 +3690,13 @@
       <c r="Z46" s="1">
         <v>30.9</v>
       </c>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AD46" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="9"/>
@@ -3404,10 +3725,11 @@
       <c r="Z47" s="9"/>
       <c r="AA47" s="9"/>
       <c r="AB47" s="9"/>
-    </row>
-    <row r="48" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD47" s="9"/>
+    </row>
+    <row r="48" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B48" s="19">
         <v>1</v>
@@ -3416,13 +3738,13 @@
         <v>2</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O48" s="13">
         <v>0.33</v>
@@ -3453,27 +3775,30 @@
         <v>240</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="49" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="AD48" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B49" s="19">
         <v>1</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O49" s="13">
         <v>0.33</v>
@@ -3504,12 +3829,15 @@
         <v>45</v>
       </c>
       <c r="AB49" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="50" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+      <c r="AD49" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="15"/>
@@ -3538,28 +3866,29 @@
       <c r="Z50" s="15"/>
       <c r="AA50" s="15"/>
       <c r="AB50" s="15"/>
-    </row>
-    <row r="51" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD50" s="15"/>
+    </row>
+    <row r="51" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B51" s="19">
         <v>1</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>200</v>
+        <v>296</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="O51" s="1">
         <v>0.9</v>
@@ -3595,31 +3924,34 @@
       <c r="Z51" s="1">
         <v>42.5</v>
       </c>
-    </row>
-    <row r="52" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD51" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B52" s="19">
         <v>1</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>4</v>
+        <v>275</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="O52" s="1">
         <v>0.9</v>
@@ -3655,31 +3987,34 @@
       <c r="Z52" s="1">
         <v>47.5</v>
       </c>
-    </row>
-    <row r="53" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD52" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B53" s="19">
         <v>1</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>203</v>
+        <v>298</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="O53" s="1">
         <v>0.9</v>
@@ -3715,10 +4050,13 @@
       <c r="Z53" s="1">
         <v>47.5</v>
       </c>
-    </row>
-    <row r="54" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD53" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="15"/>
@@ -3747,25 +4085,26 @@
       <c r="Z54" s="15"/>
       <c r="AA54" s="15"/>
       <c r="AB54" s="15"/>
-    </row>
-    <row r="55" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
-        <v>181</v>
+      <c r="AD54" s="15"/>
+    </row>
+    <row r="55" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="B55" s="19">
         <v>1</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>154</v>
+        <v>256</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>56</v>
+        <v>266</v>
       </c>
       <c r="O55" s="1">
         <v>0.94</v>
@@ -3774,34 +4113,31 @@
         <v>1</v>
       </c>
       <c r="S55" s="1">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="T55" s="19"/>
-      <c r="AA55" s="1">
-        <v>4</v>
-      </c>
-      <c r="AB55" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="56" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD55" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B56" s="19">
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>59</v>
+        <v>266</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O56" s="1">
         <v>0.94</v>
@@ -3816,25 +4152,28 @@
       <c r="AA56" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD56" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B57" s="19">
         <v>1</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>156</v>
+        <v>255</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>59</v>
+        <v>267</v>
       </c>
       <c r="O57" s="1">
         <v>0.94</v>
@@ -3846,25 +4185,28 @@
         <v>1.6</v>
       </c>
       <c r="T57" s="19"/>
-    </row>
-    <row r="58" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>181</v>
+      <c r="AD57" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="11" t="s">
+        <v>167</v>
       </c>
       <c r="B58" s="19">
         <v>1</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>155</v>
+        <v>253</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>56</v>
+        <v>267</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="O58" s="1">
         <v>0.94</v>
@@ -3873,13 +4215,22 @@
         <v>1</v>
       </c>
       <c r="S58" s="1">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="T58" s="19"/>
-    </row>
-    <row r="59" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA58" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB58" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD58" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="15"/>
@@ -3908,28 +4259,29 @@
       <c r="Z59" s="15"/>
       <c r="AA59" s="15"/>
       <c r="AB59" s="15"/>
-    </row>
-    <row r="60" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD59" s="15"/>
+    </row>
+    <row r="60" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B60" s="19">
         <v>1</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O60" s="1">
         <v>1</v>
@@ -3938,31 +4290,31 @@
         <v>1</v>
       </c>
       <c r="Q60" s="1">
-        <v>0</v>
-      </c>
-      <c r="R60" s="1">
         <v>1</v>
       </c>
       <c r="T60" s="19"/>
-    </row>
-    <row r="61" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD60" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B61" s="19">
         <v>1</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O61" s="1">
         <v>2.8</v>
@@ -3971,9 +4323,6 @@
         <v>2.8</v>
       </c>
       <c r="Q61" s="1">
-        <v>0</v>
-      </c>
-      <c r="R61" s="1">
         <v>1</v>
       </c>
       <c r="S61" s="1">
@@ -3983,30 +4332,33 @@
         <v>20</v>
       </c>
       <c r="AB61" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="62" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="AD61" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B62" s="19">
         <v>1</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>144</v>
+        <v>236</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>45</v>
+        <v>280</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O62" s="1">
         <v>0.9</v>
@@ -4015,9 +4367,6 @@
         <v>0.9</v>
       </c>
       <c r="Q62" s="1">
-        <v>0</v>
-      </c>
-      <c r="R62" s="1">
         <v>1</v>
       </c>
       <c r="S62" s="1">
@@ -4036,28 +4385,31 @@
       <c r="Z62" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="63" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD62" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B63" s="19">
         <v>1</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>142</v>
+        <v>237</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>31</v>
+        <v>279</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O63" s="1">
         <v>0.9</v>
@@ -4066,9 +4418,6 @@
         <v>0.9</v>
       </c>
       <c r="Q63" s="1">
-        <v>0</v>
-      </c>
-      <c r="R63" s="1">
         <v>1</v>
       </c>
       <c r="S63" s="1">
@@ -4087,28 +4436,31 @@
       <c r="Z63" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="64" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD63" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B64" s="19">
         <v>1</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>135</v>
+        <v>238</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O64" s="1">
         <v>0.9</v>
@@ -4117,9 +4469,6 @@
         <v>0.9</v>
       </c>
       <c r="Q64" s="1">
-        <v>0</v>
-      </c>
-      <c r="R64" s="1">
         <v>1</v>
       </c>
       <c r="S64" s="1">
@@ -4138,25 +4487,28 @@
       <c r="Z64" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="65" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD64" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B65" s="19">
         <v>1</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>145</v>
+        <v>239</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O65" s="1">
         <v>0.9</v>
@@ -4165,9 +4517,6 @@
         <v>0.9</v>
       </c>
       <c r="Q65" s="1">
-        <v>0</v>
-      </c>
-      <c r="R65" s="1">
         <v>1</v>
       </c>
       <c r="S65" s="1">
@@ -4186,25 +4535,28 @@
       <c r="Z65" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="66" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD65" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B66" s="19">
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>152</v>
+        <v>240</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O66" s="1">
         <v>0.98</v>
@@ -4213,45 +4565,45 @@
         <v>0.98</v>
       </c>
       <c r="Q66" s="1">
-        <v>0</v>
-      </c>
-      <c r="R66" s="1">
         <v>1</v>
       </c>
       <c r="S66" s="1">
-        <v>13</v>
+        <v>1.5</v>
       </c>
       <c r="T66" s="19">
         <v>20</v>
       </c>
       <c r="AB66" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="67" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="AD66" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B67" s="19">
         <v>1</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>143</v>
+        <v>241</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>45</v>
+        <v>280</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O67" s="1">
         <v>0.89</v>
@@ -4284,31 +4636,34 @@
       <c r="Z67" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="68" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD67" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B68" s="19">
         <v>1</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>122</v>
+        <v>242</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>4</v>
+        <v>275</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O68" s="1">
         <v>0.89</v>
@@ -4341,28 +4696,31 @@
       <c r="Z68" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="69" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD68" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B69" s="19">
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O69" s="1">
         <v>0.89</v>
@@ -4395,31 +4753,34 @@
       <c r="Z69" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="70" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD69" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B70" s="19">
         <v>1</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>133</v>
+        <v>247</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O70" s="1">
         <v>0.9</v>
@@ -4452,28 +4813,31 @@
       <c r="Z70" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="71" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD70" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B71" s="19">
         <v>1</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>209</v>
+        <v>248</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>4</v>
+        <v>275</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O71" s="1">
         <v>0.9</v>
@@ -4482,9 +4846,6 @@
         <v>0.9</v>
       </c>
       <c r="Q71" s="1">
-        <v>0</v>
-      </c>
-      <c r="R71" s="1">
         <v>1</v>
       </c>
       <c r="S71" s="1">
@@ -4497,31 +4858,34 @@
       <c r="V71" s="1">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="72" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD71" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B72" s="19">
         <v>1</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>4</v>
+        <v>275</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O72" s="1">
         <v>0.89</v>
@@ -4557,28 +4921,31 @@
       <c r="Z72" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="73" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD72" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B73" s="19">
         <v>1</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O73" s="1">
         <v>0.89</v>
@@ -4614,31 +4981,34 @@
       <c r="Z73" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="74" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD73" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B74" s="19">
         <v>1</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O74" s="1">
         <v>0.9</v>
@@ -4674,31 +5044,34 @@
       <c r="Z74" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="75" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD74" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B75" s="19">
         <v>1</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>34</v>
+        <v>278</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O75" s="1">
         <v>0.55000000000000004</v>
@@ -4731,31 +5104,34 @@
       <c r="Z75" s="1">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="76" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD75" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="76" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B76" s="19">
         <v>1</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>134</v>
+        <v>252</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O76" s="1">
         <v>0.9</v>
@@ -4788,25 +5164,28 @@
       <c r="Z76" s="1">
         <v>12.1</v>
       </c>
-    </row>
-    <row r="77" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD76" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B77" s="19">
         <v>1</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>257</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>182</v>
+        <v>263</v>
       </c>
       <c r="O77" s="1">
         <v>0.99</v>
@@ -4818,28 +5197,28 @@
         <v>1.4</v>
       </c>
       <c r="T77" s="19"/>
-      <c r="AA77" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD77" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B78" s="19">
         <v>1</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>172</v>
+        <v>258</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>182</v>
+        <v>263</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="O78" s="1">
         <v>0.99</v>
@@ -4851,25 +5230,31 @@
         <v>1.4</v>
       </c>
       <c r="T78" s="19"/>
-    </row>
-    <row r="79" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA78" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD78" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B79" s="19">
         <v>1</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>173</v>
+        <v>259</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>182</v>
+        <v>264</v>
       </c>
       <c r="O79" s="1">
         <v>0.99</v>
@@ -4881,31 +5266,28 @@
         <v>1.7</v>
       </c>
       <c r="T79" s="19"/>
-      <c r="AA79" s="1">
-        <v>100</v>
-      </c>
-      <c r="AB79" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="80" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD79" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B80" s="19">
         <v>1</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>174</v>
+        <v>260</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>182</v>
+        <v>264</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="O80" s="1">
         <v>0.99</v>
@@ -4917,25 +5299,34 @@
         <v>1.7</v>
       </c>
       <c r="T80" s="19"/>
-    </row>
-    <row r="81" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA80" s="1">
+        <v>100</v>
+      </c>
+      <c r="AB80" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AD80" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B81" s="19">
         <v>1</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>175</v>
+        <v>261</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>182</v>
+        <v>265</v>
       </c>
       <c r="O81" s="1">
         <v>0.99</v>
@@ -4947,28 +5338,28 @@
         <v>2</v>
       </c>
       <c r="T81" s="19"/>
-      <c r="AA81" s="1">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="82" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD81" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="82" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B82" s="19">
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>182</v>
+        <v>265</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="O82" s="1">
         <v>0.99</v>
@@ -4980,10 +5371,16 @@
         <v>2</v>
       </c>
       <c r="T82" s="19"/>
-    </row>
-    <row r="83" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA82" s="1">
+        <v>450</v>
+      </c>
+      <c r="AD82" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="83" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="B83" s="18"/>
       <c r="C83" s="15"/>
@@ -5012,25 +5409,26 @@
       <c r="Z83" s="15"/>
       <c r="AA83" s="15"/>
       <c r="AB83" s="15"/>
-    </row>
-    <row r="84" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD83" s="15"/>
+    </row>
+    <row r="84" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B84" s="19">
         <v>1</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F84" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K84" s="1" t="s">
         <v>3</v>
@@ -5044,25 +5442,28 @@
       <c r="T84" s="19">
         <v>10</v>
       </c>
-    </row>
-    <row r="85" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD84" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="85" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B85" s="19">
         <v>1</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="F85" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K85" s="1" t="s">
         <v>3</v>
@@ -5076,19 +5477,22 @@
       <c r="T85" s="19">
         <v>20</v>
       </c>
-    </row>
-    <row r="86" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD85" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="86" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B86" s="19">
         <v>1</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="E86" s="1" t="b">
         <v>1</v>
@@ -5097,7 +5501,7 @@
         <v>3</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O86" s="1">
         <v>1</v>
@@ -5109,19 +5513,22 @@
         <v>2000</v>
       </c>
       <c r="T86" s="19"/>
-    </row>
-    <row r="87" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD86" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="87" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B87" s="19">
         <v>1</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E87" s="1" t="b">
         <v>1</v>
@@ -5130,7 +5537,7 @@
         <v>3</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O87" s="1">
         <v>1</v>
@@ -5142,19 +5549,22 @@
         <v>1000</v>
       </c>
       <c r="T87" s="19"/>
-    </row>
-    <row r="88" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD87" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="88" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B88" s="19">
         <v>1</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E88" s="1" t="b">
         <v>1</v>
@@ -5163,7 +5573,7 @@
         <v>3</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O88" s="1">
         <v>1</v>
@@ -5175,10 +5585,13 @@
         <v>400</v>
       </c>
       <c r="T88" s="19"/>
-    </row>
-    <row r="89" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD88" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="89" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="15"/>
@@ -5207,25 +5620,26 @@
       <c r="Z89" s="15"/>
       <c r="AA89" s="15"/>
       <c r="AB89" s="15"/>
-    </row>
-    <row r="90" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD89" s="15"/>
+    </row>
+    <row r="90" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B90" s="19">
         <v>1</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>64</v>
+        <v>268</v>
       </c>
       <c r="O90" s="1">
         <v>0.61</v>
@@ -5244,27 +5658,30 @@
         <v>15</v>
       </c>
       <c r="AB90" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="91" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="AD90" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="91" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B91" s="19">
         <v>1</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>64</v>
+        <v>268</v>
       </c>
       <c r="O91" s="1">
         <v>0.8</v>
@@ -5283,196 +5700,182 @@
         <v>25</v>
       </c>
       <c r="AB91" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="92" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B92" s="19">
-        <v>1</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AD91" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="92" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>167</v>
+      </c>
+      <c r="B92" s="21">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s">
+        <v>299</v>
+      </c>
+      <c r="D92" t="s">
+        <v>300</v>
+      </c>
+      <c r="J92" t="s">
+        <v>268</v>
+      </c>
+      <c r="K92" t="s">
+        <v>49</v>
+      </c>
+      <c r="O92">
+        <v>0.6</v>
+      </c>
+      <c r="Q92">
+        <v>0.4</v>
+      </c>
+      <c r="R92">
+        <v>1</v>
+      </c>
+      <c r="S92">
+        <v>1.6</v>
+      </c>
+      <c r="T92"/>
+      <c r="AN92" s="24"/>
+    </row>
+    <row r="93" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B93" s="19">
+        <v>1</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="O92" s="1">
-        <f>P92-0.03</f>
+      <c r="D93" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O93" s="1">
+        <f>P93-0.03</f>
         <v>0.31999999999999995</v>
       </c>
-      <c r="P92" s="1">
+      <c r="P93" s="1">
         <v>0.35</v>
       </c>
-      <c r="Q92" s="1">
+      <c r="Q93" s="1">
         <v>0.5</v>
       </c>
-      <c r="R92" s="1">
-        <v>1</v>
-      </c>
-      <c r="S92" s="1">
+      <c r="R93" s="1">
+        <v>1</v>
+      </c>
+      <c r="S93" s="1">
         <v>5</v>
       </c>
-      <c r="T92" s="19"/>
-      <c r="Y92" s="1">
+      <c r="T93" s="19"/>
+      <c r="Y93" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="93" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B93" s="19">
-        <v>1</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O93" s="1">
-        <v>1</v>
-      </c>
-      <c r="P93" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q93" s="1">
-        <v>0</v>
-      </c>
-      <c r="R93" s="1">
-        <v>1</v>
-      </c>
-      <c r="S93" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="T93" s="19"/>
-      <c r="AA93" s="16">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="94" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD93" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="94" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B94" s="19">
         <v>1</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>164</v>
+        <v>269</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>64</v>
+        <v>273</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>89</v>
+        <v>268</v>
       </c>
       <c r="O94" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="P94" s="1">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="Q94" s="1">
-        <v>0</v>
-      </c>
-      <c r="R94" s="1">
         <v>1</v>
       </c>
       <c r="S94" s="1">
         <v>1.5</v>
       </c>
       <c r="T94" s="19"/>
-      <c r="AA94" s="16"/>
-    </row>
-    <row r="95" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA94" s="16">
+        <v>24</v>
+      </c>
+      <c r="AD94" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="95" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B95" s="19">
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>88</v>
+        <v>268</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>64</v>
+        <v>273</v>
       </c>
       <c r="O95" s="1">
-        <v>1</v>
-      </c>
-      <c r="P95" s="1">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="Q95" s="1">
-        <v>0</v>
-      </c>
-      <c r="R95" s="1">
         <v>1</v>
       </c>
       <c r="S95" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T95" s="19"/>
-      <c r="Y95" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA95" s="16">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="96" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA95" s="16"/>
+      <c r="AD95" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="96" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B96" s="19">
         <v>1</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>162</v>
+        <v>271</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>64</v>
+        <v>274</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>88</v>
+        <v>268</v>
       </c>
       <c r="O96" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="P96" s="1">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="Q96" s="1">
-        <v>0</v>
-      </c>
-      <c r="R96" s="1">
         <v>1</v>
       </c>
       <c r="S96" s="1">
@@ -5482,14 +5885,52 @@
       <c r="Y96" s="1">
         <v>0</v>
       </c>
-      <c r="AA96" s="16"/>
+      <c r="AA96" s="16">
+        <v>924</v>
+      </c>
+      <c r="AD96" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B97" s="19">
+        <v>1</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="O97" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="Q97" s="1">
+        <v>1</v>
+      </c>
+      <c r="S97" s="1">
+        <v>2</v>
+      </c>
+      <c r="T97" s="19"/>
+      <c r="Y97" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="16"/>
+      <c r="AD97" s="1" t="s">
+        <v>148</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:AA43" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:AA43">
-      <sortCondition descending="1" ref="D1:D43"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="C1:AA43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/src_files/data_files/unittypedata_compilation.xlsx
+++ b/src_files/data_files/unittypedata_compilation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025226CE-07DA-49AD-A46B-B4FF1144D435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2924A72-2634-45FF-A8A9-EDBF94A2B274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -751,12 +751,6 @@
     <t>##maxRampDown</t>
   </si>
   <si>
-    <t>##rampUpCost</t>
-  </si>
-  <si>
-    <t>##rampDownCost</t>
-  </si>
-  <si>
     <t>## Description</t>
   </si>
   <si>
@@ -974,6 +968,12 @@
   </si>
   <si>
     <t>ETS</t>
+  </si>
+  <si>
+    <t>rampUpCost</t>
+  </si>
+  <si>
+    <t>rampDownCost</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1406,7 @@
         <v>88</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>176</v>
@@ -1472,10 +1472,10 @@
         <v>86</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>227</v>
+        <v>300</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>228</v>
+        <v>301</v>
       </c>
       <c r="AA1" s="3" t="s">
         <v>169</v>
@@ -1484,7 +1484,7 @@
         <v>224</v>
       </c>
       <c r="AD1" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1606,7 +1606,7 @@
         <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>82</v>
@@ -1759,7 +1759,7 @@
         <v>76</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>44</v>
@@ -1798,7 +1798,7 @@
         <v>77</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>49</v>
@@ -1837,7 +1837,7 @@
         <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>54</v>
@@ -1876,7 +1876,7 @@
         <v>55</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>49</v>
@@ -1951,10 +1951,10 @@
         <v>125</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>49</v>
@@ -2002,13 +2002,13 @@
         <v>32</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>49</v>
@@ -2059,10 +2059,10 @@
         <v>126</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>49</v>
@@ -2110,11 +2110,11 @@
         <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>49</v>
@@ -2165,10 +2165,10 @@
         <v>98</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>49</v>
@@ -2216,11 +2216,11 @@
         <v>15</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>49</v>
@@ -2271,10 +2271,10 @@
         <v>97</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>49</v>
@@ -2325,10 +2325,10 @@
         <v>99</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>49</v>
@@ -2379,7 +2379,7 @@
         <v>95</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>49</v>
@@ -2427,13 +2427,13 @@
         <v>27</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>49</v>
@@ -2481,13 +2481,13 @@
         <v>29</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>49</v>
@@ -2535,13 +2535,13 @@
         <v>28</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>49</v>
@@ -2589,10 +2589,10 @@
         <v>172</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>49</v>
@@ -2640,13 +2640,13 @@
         <v>9</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>49</v>
@@ -2694,13 +2694,13 @@
         <v>10</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>49</v>
@@ -2748,13 +2748,13 @@
         <v>5</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>49</v>
@@ -2802,13 +2802,13 @@
         <v>4</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>49</v>
@@ -2856,13 +2856,13 @@
         <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>49</v>
@@ -2910,13 +2910,13 @@
         <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>49</v>
@@ -2964,10 +2964,10 @@
         <v>170</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>49</v>
@@ -3018,10 +3018,10 @@
         <v>110</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>49</v>
@@ -3072,10 +3072,10 @@
         <v>109</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>49</v>
@@ -3126,10 +3126,10 @@
         <v>117</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>49</v>
@@ -3180,10 +3180,10 @@
         <v>118</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>49</v>
@@ -3234,10 +3234,10 @@
         <v>114</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>49</v>
@@ -3288,10 +3288,10 @@
         <v>113</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>49</v>
@@ -3339,10 +3339,10 @@
         <v>174</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>49</v>
@@ -3393,10 +3393,10 @@
         <v>112</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K41" s="1" t="s">
         <v>49</v>
@@ -3447,10 +3447,10 @@
         <v>111</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>49</v>
@@ -3501,10 +3501,10 @@
         <v>115</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>49</v>
@@ -3585,13 +3585,13 @@
         <v>7</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>49</v>
@@ -3648,10 +3648,10 @@
         <v>116</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>49</v>
@@ -3879,10 +3879,10 @@
         <v>185</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>49</v>
@@ -3939,13 +3939,13 @@
         <v>184</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>49</v>
@@ -4002,13 +4002,13 @@
         <v>188</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>49</v>
@@ -4098,13 +4098,13 @@
         <v>52</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>49</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O55" s="1">
         <v>0.94</v>
@@ -4131,10 +4131,10 @@
         <v>51</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>49</v>
@@ -4167,13 +4167,13 @@
         <v>79</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="O57" s="1">
         <v>0.94</v>
@@ -4200,10 +4200,10 @@
         <v>78</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>49</v>
@@ -4349,13 +4349,13 @@
         <v>70</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>168</v>
@@ -4400,13 +4400,13 @@
         <v>34</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>168</v>
@@ -4451,13 +4451,13 @@
         <v>35</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>168</v>
@@ -4502,10 +4502,10 @@
         <v>36</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>168</v>
@@ -4550,7 +4550,7 @@
         <v>50</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>49</v>
@@ -4591,13 +4591,13 @@
         <v>39</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K67" s="1" t="s">
         <v>49</v>
@@ -4651,13 +4651,13 @@
         <v>38</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>49</v>
@@ -4711,10 +4711,10 @@
         <v>37</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>49</v>
@@ -4768,13 +4768,13 @@
         <v>33</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>49</v>
@@ -4828,13 +4828,13 @@
         <v>192</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>168</v>
@@ -4873,13 +4873,13 @@
         <v>194</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K72" s="1" t="s">
         <v>49</v>
@@ -4936,10 +4936,10 @@
         <v>196</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K73" s="1" t="s">
         <v>49</v>
@@ -4996,13 +4996,13 @@
         <v>198</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>49</v>
@@ -5062,10 +5062,10 @@
         <v>191</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>49</v>
@@ -5119,13 +5119,13 @@
         <v>69</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K76" s="1" t="s">
         <v>49</v>
@@ -5179,13 +5179,13 @@
         <v>63</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>168</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O77" s="1">
         <v>0.99</v>
@@ -5212,10 +5212,10 @@
         <v>62</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K78" s="1" t="s">
         <v>168</v>
@@ -5248,13 +5248,13 @@
         <v>65</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>168</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O79" s="1">
         <v>0.99</v>
@@ -5281,10 +5281,10 @@
         <v>66</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K80" s="1" t="s">
         <v>168</v>
@@ -5320,13 +5320,13 @@
         <v>67</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>168</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="O81" s="1">
         <v>0.99</v>
@@ -5353,10 +5353,10 @@
         <v>68</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="K82" s="1" t="s">
         <v>168</v>
@@ -5639,7 +5639,7 @@
         <v>49</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="O90" s="1">
         <v>0.61</v>
@@ -5681,7 +5681,7 @@
         <v>49</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="O91" s="1">
         <v>0.8</v>
@@ -5714,13 +5714,13 @@
         <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D92" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J92" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K92" t="s">
         <v>49</v>
@@ -5754,7 +5754,7 @@
         <v>147</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K93" s="1" t="s">
         <v>49</v>
@@ -5794,13 +5794,13 @@
         <v>75</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="O94" s="1">
         <v>1</v>
@@ -5830,13 +5830,13 @@
         <v>74</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="O95" s="1">
         <v>0.99</v>
@@ -5864,13 +5864,13 @@
         <v>73</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="O96" s="1">
         <v>1</v>
@@ -5903,13 +5903,13 @@
         <v>72</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="K97" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>274</v>
       </c>
       <c r="O97" s="1">
         <v>0.99</v>
